--- a/Документы/НБ.xlsx
+++ b/Документы/НБ.xlsx
@@ -24,112 +24,112 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
   <si>
-    <t>Регион №47</t>
-  </si>
-  <si>
-    <t>Приглашаем на работу №24</t>
-  </si>
-  <si>
-    <t>Царкоунае слова №25</t>
-  </si>
-  <si>
-    <t>Газета пенсионера №25</t>
-  </si>
-  <si>
-    <t>Здоровье пенсионера №25</t>
-  </si>
-  <si>
-    <t>Рэкламны дзяржынск №24</t>
-  </si>
-  <si>
-    <t>Родны край №45</t>
-  </si>
-  <si>
-    <t>Слава працы №44</t>
-  </si>
-  <si>
-    <t>Астравецкая прауда №46</t>
-  </si>
-  <si>
-    <t>Ашмянски весник №46</t>
-  </si>
-  <si>
-    <t>Працоуная слава №24</t>
-  </si>
-  <si>
-    <t>Светлы шлях №25</t>
-  </si>
-  <si>
-    <t>Маладзечанская газета №44</t>
-  </si>
-  <si>
-    <t>Новае жыцце №46</t>
-  </si>
-  <si>
-    <t>Шлях перамоги №44</t>
-  </si>
-  <si>
-    <t>Полымя №48</t>
-  </si>
-  <si>
-    <t>Перамога №47</t>
-  </si>
-  <si>
-    <t>Лидская газета №46</t>
-  </si>
-  <si>
-    <t>Регион №48</t>
-  </si>
-  <si>
-    <t>Работа для вас №70</t>
-  </si>
-  <si>
-    <t>Работа для вас №71</t>
-  </si>
-  <si>
-    <t>Принимаем на работу №24</t>
-  </si>
-  <si>
-    <t>Ашмянски весник №47</t>
-  </si>
-  <si>
-    <t>Астравецкая прауда №47</t>
-  </si>
-  <si>
-    <t>Родны край №46</t>
-  </si>
-  <si>
-    <t>Азбука дома №24</t>
-  </si>
-  <si>
-    <t>Маладзечанская газета №45</t>
-  </si>
-  <si>
-    <t>Новае жыцце №47</t>
-  </si>
-  <si>
-    <t>Перамога №48</t>
-  </si>
-  <si>
-    <t>Слава працы №45</t>
-  </si>
-  <si>
-    <t>Шлях перамоги №45</t>
-  </si>
-  <si>
-    <t>ПАК №25</t>
-  </si>
-  <si>
-    <t>Женская газета №25</t>
-  </si>
-  <si>
-    <t>Досуг пенсионера №25</t>
-  </si>
-  <si>
-    <t>Лидская газета №47</t>
-  </si>
-  <si>
-    <t>Работа для вас №72</t>
+    <t>Берега №6</t>
+  </si>
+  <si>
+    <t>Гороскоп №6</t>
+  </si>
+  <si>
+    <t>Регион №49</t>
+  </si>
+  <si>
+    <t>Приглашаем на работу №25</t>
+  </si>
+  <si>
+    <t>Царкоунае слова №26</t>
+  </si>
+  <si>
+    <t>Газета пенсионера №26</t>
+  </si>
+  <si>
+    <t>Здоровье пенсионера №26</t>
+  </si>
+  <si>
+    <t>Вестник профсоюза БЕЛПРОФМАШ №2</t>
+  </si>
+  <si>
+    <t>БЦК-ИНФО №6</t>
+  </si>
+  <si>
+    <t>Рэкламны дзяржынск №25</t>
+  </si>
+  <si>
+    <t>Родны край №47</t>
+  </si>
+  <si>
+    <t>Слава працы №46</t>
+  </si>
+  <si>
+    <t>Астравецкая прауда №48</t>
+  </si>
+  <si>
+    <t>Ашмянски весник №48</t>
+  </si>
+  <si>
+    <t>Працоуная слава №25</t>
+  </si>
+  <si>
+    <t>Светлы шлях №26</t>
+  </si>
+  <si>
+    <t>Маладзечанская газета №46</t>
+  </si>
+  <si>
+    <t>Новае жыцце №48</t>
+  </si>
+  <si>
+    <t>Шлях перамоги №46</t>
+  </si>
+  <si>
+    <t>Полымя №50</t>
+  </si>
+  <si>
+    <t>Перамога №49</t>
+  </si>
+  <si>
+    <t>Лидская газета №48</t>
+  </si>
+  <si>
+    <t>Регион №50</t>
+  </si>
+  <si>
+    <t>Работа для вас №73</t>
+  </si>
+  <si>
+    <t>Работа для вас №74</t>
+  </si>
+  <si>
+    <t>Принимаем на работу №25</t>
+  </si>
+  <si>
+    <t>Ашмянски весник №49</t>
+  </si>
+  <si>
+    <t>Астравецкая прауда №49</t>
+  </si>
+  <si>
+    <t>Родны край №48</t>
+  </si>
+  <si>
+    <t>Азбука дома №25</t>
+  </si>
+  <si>
+    <t>Перамога №50</t>
+  </si>
+  <si>
+    <t>Регион №51</t>
+  </si>
+  <si>
+    <t>ПАК №26</t>
+  </si>
+  <si>
+    <t>Женская газета №26</t>
+  </si>
+  <si>
+    <t>Досуг пенсионера №26</t>
+  </si>
+  <si>
+    <t>Работа для вас №75</t>
   </si>
 </sst>
 </file>
@@ -493,7 +493,7 @@
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
       <c r="C3" s="1">
-        <v>823</v>
+        <v>859</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="5" t="s">
@@ -503,7 +503,7 @@
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="2"/>
       <c r="C4" s="1">
-        <v>824</v>
+        <v>860</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="5" t="s">
@@ -513,7 +513,7 @@
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="2"/>
       <c r="C5" s="1">
-        <v>825</v>
+        <v>861</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="5" t="s">
@@ -523,7 +523,7 @@
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="2"/>
       <c r="C6" s="1">
-        <v>826</v>
+        <v>862</v>
       </c>
       <c r="D6" s="2"/>
       <c r="E6" s="5" t="s">
@@ -533,7 +533,7 @@
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="2"/>
       <c r="C7" s="1">
-        <v>827</v>
+        <v>863</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="5" t="s">
@@ -543,7 +543,7 @@
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="2"/>
       <c r="C8" s="1">
-        <v>828</v>
+        <v>864</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="5" t="s">
@@ -553,7 +553,7 @@
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="2"/>
       <c r="C9" s="1">
-        <v>829</v>
+        <v>865</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="5" t="s">
@@ -563,7 +563,7 @@
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
       <c r="C10" s="1">
-        <v>830</v>
+        <v>866</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="5" t="s">
@@ -573,7 +573,7 @@
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="2"/>
       <c r="C11" s="1">
-        <v>831</v>
+        <v>867</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="5" t="s">
@@ -583,7 +583,7 @@
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" s="2"/>
       <c r="C12" s="1">
-        <v>832</v>
+        <v>868</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="5" t="s">
@@ -593,7 +593,7 @@
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
       <c r="C13" s="1">
-        <v>833</v>
+        <v>869</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="5" t="s">
@@ -603,7 +603,7 @@
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
       <c r="C14" s="1">
-        <v>834</v>
+        <v>870</v>
       </c>
       <c r="D14" s="2"/>
       <c r="E14" s="5" t="s">
@@ -613,7 +613,7 @@
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
       <c r="C15" s="1">
-        <v>835</v>
+        <v>871</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="5" t="s">
@@ -623,7 +623,7 @@
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
       <c r="C16" s="1">
-        <v>836</v>
+        <v>872</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="5" t="s">
@@ -633,7 +633,7 @@
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
       <c r="C17" s="1">
-        <v>837</v>
+        <v>873</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="5" t="s">
@@ -643,7 +643,7 @@
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
       <c r="C18" s="1">
-        <v>838</v>
+        <v>874</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="5" t="s">
@@ -653,7 +653,7 @@
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="2"/>
       <c r="C19" s="1">
-        <v>839</v>
+        <v>875</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="5" t="s">
@@ -663,7 +663,7 @@
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="2"/>
       <c r="C20" s="1">
-        <v>840</v>
+        <v>876</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
@@ -673,7 +673,7 @@
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="2"/>
       <c r="C21" s="1">
-        <v>841</v>
+        <v>877</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
@@ -683,7 +683,7 @@
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="2"/>
       <c r="C22" s="1">
-        <v>842</v>
+        <v>878</v>
       </c>
       <c r="D22" s="2"/>
       <c r="E22" s="2" t="s">
@@ -693,7 +693,7 @@
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="2"/>
       <c r="C23" s="1">
-        <v>843</v>
+        <v>879</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2" t="s">
@@ -703,7 +703,7 @@
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="2"/>
       <c r="C24" s="1">
-        <v>844</v>
+        <v>880</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
@@ -713,7 +713,7 @@
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B25" s="2"/>
       <c r="C25" s="1">
-        <v>845</v>
+        <v>881</v>
       </c>
       <c r="D25" s="2"/>
       <c r="E25" s="2" t="s">
@@ -723,7 +723,7 @@
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B26" s="2"/>
       <c r="C26" s="1">
-        <v>846</v>
+        <v>882</v>
       </c>
       <c r="D26" s="2"/>
       <c r="E26" s="2" t="s">
@@ -733,7 +733,7 @@
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
       <c r="C27" s="1">
-        <v>847</v>
+        <v>883</v>
       </c>
       <c r="D27" s="2"/>
       <c r="E27" s="2" t="s">
@@ -743,7 +743,7 @@
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="2"/>
       <c r="C28" s="1">
-        <v>848</v>
+        <v>884</v>
       </c>
       <c r="D28" s="2"/>
       <c r="E28" s="2" t="s">
@@ -753,7 +753,7 @@
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="2"/>
       <c r="C29" s="1">
-        <v>849</v>
+        <v>885</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" s="2" t="s">
@@ -763,7 +763,7 @@
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="2"/>
       <c r="C30" s="1">
-        <v>850</v>
+        <v>886</v>
       </c>
       <c r="D30" s="2"/>
       <c r="E30" s="2" t="s">
@@ -773,7 +773,7 @@
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="2"/>
       <c r="C31" s="1">
-        <v>851</v>
+        <v>887</v>
       </c>
       <c r="D31" s="2"/>
       <c r="E31" s="2" t="s">
@@ -783,7 +783,7 @@
     <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="2"/>
       <c r="C32" s="1">
-        <v>852</v>
+        <v>888</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="s">
@@ -793,7 +793,7 @@
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="2"/>
       <c r="C33" s="1">
-        <v>853</v>
+        <v>889</v>
       </c>
       <c r="D33" s="2"/>
       <c r="E33" s="2" t="s">
@@ -803,7 +803,7 @@
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="2"/>
       <c r="C34" s="1">
-        <v>854</v>
+        <v>890</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="5" t="s">
@@ -813,7 +813,7 @@
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="2"/>
       <c r="C35" s="1">
-        <v>855</v>
+        <v>891</v>
       </c>
       <c r="D35" s="2"/>
       <c r="E35" s="5" t="s">
@@ -823,7 +823,7 @@
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B36" s="2"/>
       <c r="C36" s="1">
-        <v>856</v>
+        <v>892</v>
       </c>
       <c r="D36" s="2"/>
       <c r="E36" s="5" t="s">
@@ -833,7 +833,7 @@
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B37" s="2"/>
       <c r="C37" s="1">
-        <v>857</v>
+        <v>893</v>
       </c>
       <c r="D37" s="2"/>
       <c r="E37" s="5" t="s">
@@ -843,7 +843,7 @@
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B38" s="2"/>
       <c r="C38" s="1">
-        <v>858</v>
+        <v>894</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="5" t="s">
